--- a/sensor_data.xlsx
+++ b/sensor_data.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,22 +429,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Time</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>MW</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Gate_Angle</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Viscosity</t>
         </is>
@@ -445,13 +457,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.039999999999999</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>40.8</v>
+        <v>40.42</v>
       </c>
       <c r="D2" t="n">
-        <v>51.51</v>
+        <v>49.74</v>
       </c>
     </row>
     <row r="3">
@@ -461,13 +473,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.01</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>40.06</v>
+        <v>40.18</v>
       </c>
       <c r="D3" t="n">
-        <v>48.2</v>
+        <v>51.94</v>
       </c>
     </row>
     <row r="4">
@@ -477,13 +489,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8.960000000000001</v>
+        <v>9.02</v>
       </c>
       <c r="C4" t="n">
-        <v>41.13</v>
+        <v>41.58</v>
       </c>
       <c r="D4" t="n">
-        <v>50.33</v>
+        <v>50.93</v>
       </c>
     </row>
     <row r="5">
@@ -493,13 +505,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9</v>
+        <v>9.02</v>
       </c>
       <c r="C5" t="n">
-        <v>40.14</v>
+        <v>41.23</v>
       </c>
       <c r="D5" t="n">
-        <v>50.81</v>
+        <v>49.63</v>
       </c>
     </row>
     <row r="6">
@@ -509,13 +521,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.98</v>
+        <v>9.01</v>
       </c>
       <c r="C6" t="n">
-        <v>40.1</v>
+        <v>41.3</v>
       </c>
       <c r="D6" t="n">
-        <v>48.17</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="7">
@@ -525,13 +537,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.01</v>
+        <v>8.99</v>
       </c>
       <c r="C7" t="n">
-        <v>40.89</v>
+        <v>40.21</v>
       </c>
       <c r="D7" t="n">
-        <v>51.43</v>
+        <v>49.33</v>
       </c>
     </row>
     <row r="8">
@@ -541,13 +553,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.01</v>
+        <v>9.02</v>
       </c>
       <c r="C8" t="n">
-        <v>40.52</v>
+        <v>40.69</v>
       </c>
       <c r="D8" t="n">
-        <v>48.87</v>
+        <v>51.89</v>
       </c>
     </row>
     <row r="9">
@@ -557,13 +569,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8.960000000000001</v>
+        <v>8.98</v>
       </c>
       <c r="C9" t="n">
-        <v>41.03</v>
+        <v>41.41</v>
       </c>
       <c r="D9" t="n">
-        <v>48.24</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="10">
@@ -573,13 +585,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8.970000000000001</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="C10" t="n">
-        <v>40.58</v>
+        <v>41.58</v>
       </c>
       <c r="D10" t="n">
-        <v>48.63</v>
+        <v>50.81</v>
       </c>
     </row>
     <row r="11">
@@ -589,13 +601,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8.960000000000001</v>
+        <v>8.98</v>
       </c>
       <c r="C11" t="n">
-        <v>40.32</v>
+        <v>40.27</v>
       </c>
       <c r="D11" t="n">
-        <v>49.47</v>
+        <v>50.54</v>
       </c>
     </row>
     <row r="12">
@@ -605,13 +617,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>9</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="C12" t="n">
-        <v>40.95</v>
+        <v>41.8</v>
       </c>
       <c r="D12" t="n">
-        <v>50.71</v>
+        <v>51.17</v>
       </c>
     </row>
     <row r="13">
@@ -621,13 +633,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>8.970000000000001</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="C13" t="n">
-        <v>40.07</v>
+        <v>40.52</v>
       </c>
       <c r="D13" t="n">
-        <v>48.45</v>
+        <v>49.31</v>
       </c>
     </row>
     <row r="14">
@@ -637,13 +649,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>9.039999999999999</v>
+        <v>8.98</v>
       </c>
       <c r="C14" t="n">
-        <v>40.77</v>
+        <v>41.48</v>
       </c>
       <c r="D14" t="n">
-        <v>50.71</v>
+        <v>48.51</v>
       </c>
     </row>
     <row r="15">
@@ -653,13 +665,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9</v>
+        <v>8.98</v>
       </c>
       <c r="C15" t="n">
-        <v>40.66</v>
+        <v>41.12</v>
       </c>
       <c r="D15" t="n">
-        <v>51.28</v>
+        <v>50.97</v>
       </c>
     </row>
     <row r="16">
@@ -672,10 +684,10 @@
         <v>8.99</v>
       </c>
       <c r="C16" t="n">
-        <v>40.67</v>
+        <v>41.81</v>
       </c>
       <c r="D16" t="n">
-        <v>50.01</v>
+        <v>48.24</v>
       </c>
     </row>
     <row r="17">
@@ -685,13 +697,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>9</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="C17" t="n">
-        <v>40.33</v>
+        <v>41.18</v>
       </c>
       <c r="D17" t="n">
-        <v>51.3</v>
+        <v>49.47</v>
       </c>
     </row>
     <row r="18">
@@ -701,13 +713,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>8.970000000000001</v>
+        <v>8.99</v>
       </c>
       <c r="C18" t="n">
-        <v>40.49</v>
+        <v>41.89</v>
       </c>
       <c r="D18" t="n">
-        <v>49.1</v>
+        <v>51.11</v>
       </c>
     </row>
     <row r="19">
@@ -717,13 +729,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>9.01</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="C19" t="n">
-        <v>41.16</v>
+        <v>41.14</v>
       </c>
       <c r="D19" t="n">
-        <v>48.23</v>
+        <v>50.99</v>
       </c>
     </row>
     <row r="20">
@@ -733,13 +745,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>8.960000000000001</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="C20" t="n">
-        <v>41.03</v>
+        <v>40.7</v>
       </c>
       <c r="D20" t="n">
-        <v>48.47</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="21">
@@ -749,13 +761,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>9.050000000000001</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="C21" t="n">
-        <v>41.17</v>
+        <v>41.67</v>
       </c>
       <c r="D21" t="n">
-        <v>51.69</v>
+        <v>48.18</v>
       </c>
     </row>
     <row r="22">
@@ -765,13 +777,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>9.050000000000001</v>
+        <v>9.02</v>
       </c>
       <c r="C22" t="n">
-        <v>41.67</v>
+        <v>40.62</v>
       </c>
       <c r="D22" t="n">
-        <v>48.35</v>
+        <v>50.96</v>
       </c>
     </row>
     <row r="23">
@@ -781,13 +793,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>8.460000000000001</v>
+        <v>8.52</v>
       </c>
       <c r="C23" t="n">
-        <v>64.84999999999999</v>
+        <v>64.67</v>
       </c>
       <c r="D23" t="n">
-        <v>51.05</v>
+        <v>51.59</v>
       </c>
     </row>
     <row r="24">
@@ -797,13 +809,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>8.539999999999999</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="C24" t="n">
-        <v>65.16</v>
+        <v>65.05</v>
       </c>
       <c r="D24" t="n">
-        <v>51.84</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="25">
@@ -813,13 +825,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>8.52</v>
+        <v>8.5</v>
       </c>
       <c r="C25" t="n">
-        <v>64.72</v>
+        <v>64.67</v>
       </c>
       <c r="D25" t="n">
-        <v>51.8</v>
+        <v>51.25</v>
       </c>
     </row>
     <row r="26">
@@ -829,13 +841,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>8.49</v>
+        <v>8.52</v>
       </c>
       <c r="C26" t="n">
-        <v>65.05</v>
+        <v>65.25</v>
       </c>
       <c r="D26" t="n">
-        <v>51.32</v>
+        <v>48.01</v>
       </c>
     </row>
     <row r="27">
@@ -845,13 +857,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>8.49</v>
+        <v>8.48</v>
       </c>
       <c r="C27" t="n">
-        <v>65.19</v>
+        <v>65.36</v>
       </c>
       <c r="D27" t="n">
-        <v>51.14</v>
+        <v>50.44</v>
       </c>
     </row>
     <row r="28">
@@ -861,13 +873,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>8.460000000000001</v>
+        <v>8.49</v>
       </c>
       <c r="C28" t="n">
-        <v>65.23999999999999</v>
+        <v>65.33</v>
       </c>
       <c r="D28" t="n">
-        <v>49.41</v>
+        <v>51.95</v>
       </c>
     </row>
     <row r="29">
@@ -877,13 +889,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>8.470000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="C29" t="n">
-        <v>64.73999999999999</v>
+        <v>64.5</v>
       </c>
       <c r="D29" t="n">
-        <v>50.06</v>
+        <v>49.55</v>
       </c>
     </row>
     <row r="30">
@@ -893,13 +905,13 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>8.49</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="C30" t="n">
-        <v>65.40000000000001</v>
+        <v>65.38</v>
       </c>
       <c r="D30" t="n">
-        <v>51.87</v>
+        <v>49.55</v>
       </c>
     </row>
     <row r="31">
@@ -909,13 +921,13 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>8.539999999999999</v>
+        <v>8.49</v>
       </c>
       <c r="C31" t="n">
-        <v>65.45999999999999</v>
+        <v>65.48999999999999</v>
       </c>
       <c r="D31" t="n">
-        <v>51.48</v>
+        <v>48.63</v>
       </c>
     </row>
     <row r="32">
@@ -925,13 +937,13 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>8.470000000000001</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="C32" t="n">
-        <v>64.84999999999999</v>
+        <v>64.51000000000001</v>
       </c>
       <c r="D32" t="n">
-        <v>48.97</v>
+        <v>49.92</v>
       </c>
     </row>
     <row r="33">
@@ -941,13 +953,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>8.49</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="C33" t="n">
-        <v>65.25</v>
+        <v>65.37</v>
       </c>
       <c r="D33" t="n">
-        <v>48.2</v>
+        <v>49.71</v>
       </c>
     </row>
     <row r="34">
@@ -957,13 +969,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>8.49</v>
+        <v>8.52</v>
       </c>
       <c r="C34" t="n">
-        <v>65.01000000000001</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="D34" t="n">
-        <v>48.09</v>
+        <v>49.77</v>
       </c>
     </row>
     <row r="35">
@@ -973,13 +985,13 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>8.460000000000001</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="C35" t="n">
-        <v>64.78</v>
+        <v>64.55</v>
       </c>
       <c r="D35" t="n">
-        <v>48.2</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="36">
@@ -989,13 +1001,13 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>8.48</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="C36" t="n">
-        <v>64.55</v>
+        <v>65.47</v>
       </c>
       <c r="D36" t="n">
-        <v>51.03</v>
+        <v>49.19</v>
       </c>
     </row>
     <row r="37">
@@ -1005,13 +1017,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>8.529999999999999</v>
+        <v>8.49</v>
       </c>
       <c r="C37" t="n">
-        <v>65.13</v>
+        <v>65.47</v>
       </c>
       <c r="D37" t="n">
-        <v>50.43</v>
+        <v>51.81</v>
       </c>
     </row>
     <row r="38">
@@ -1021,13 +1033,13 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>8.460000000000001</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="C38" t="n">
-        <v>65.19</v>
+        <v>65.12</v>
       </c>
       <c r="D38" t="n">
-        <v>50.01</v>
+        <v>49.68</v>
       </c>
     </row>
     <row r="39">
@@ -1040,10 +1052,10 @@
         <v>8.539999999999999</v>
       </c>
       <c r="C39" t="n">
-        <v>64.93000000000001</v>
+        <v>65.42</v>
       </c>
       <c r="D39" t="n">
-        <v>51.71</v>
+        <v>48.33</v>
       </c>
     </row>
     <row r="40">
@@ -1053,13 +1065,13 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>8.51</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="C40" t="n">
-        <v>64.91</v>
+        <v>64.51000000000001</v>
       </c>
       <c r="D40" t="n">
-        <v>48.33</v>
+        <v>48.46</v>
       </c>
     </row>
     <row r="41">
@@ -1069,13 +1081,13 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>8.539999999999999</v>
+        <v>8.49</v>
       </c>
       <c r="C41" t="n">
-        <v>65.16</v>
+        <v>65.18000000000001</v>
       </c>
       <c r="D41" t="n">
-        <v>48.23</v>
+        <v>48.75</v>
       </c>
     </row>
     <row r="42">
@@ -1085,13 +1097,13 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>8.529999999999999</v>
+        <v>8.51</v>
       </c>
       <c r="C42" t="n">
-        <v>65.09</v>
+        <v>65.27</v>
       </c>
       <c r="D42" t="n">
-        <v>49.31</v>
+        <v>49.59</v>
       </c>
     </row>
     <row r="43">
@@ -1101,13 +1113,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>9.539999999999999</v>
+        <v>9.52</v>
       </c>
       <c r="C43" t="n">
-        <v>9.949999999999999</v>
+        <v>9.73</v>
       </c>
       <c r="D43" t="n">
-        <v>51.44</v>
+        <v>48.71</v>
       </c>
     </row>
     <row r="44">
@@ -1117,13 +1129,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>9.52</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="C44" t="n">
-        <v>10.47</v>
+        <v>10.26</v>
       </c>
       <c r="D44" t="n">
-        <v>51.06</v>
+        <v>51.74</v>
       </c>
     </row>
     <row r="45">
@@ -1133,13 +1145,13 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>9.51</v>
+        <v>9.48</v>
       </c>
       <c r="C45" t="n">
-        <v>10.49</v>
+        <v>10.08</v>
       </c>
       <c r="D45" t="n">
-        <v>48.68</v>
+        <v>49.34</v>
       </c>
     </row>
     <row r="46">
@@ -1149,13 +1161,13 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>9.5</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="C46" t="n">
-        <v>10.39</v>
+        <v>10.18</v>
       </c>
       <c r="D46" t="n">
-        <v>49.23</v>
+        <v>51.46</v>
       </c>
     </row>
     <row r="47">
@@ -1165,13 +1177,13 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>9.539999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="C47" t="n">
-        <v>9.76</v>
+        <v>9.6</v>
       </c>
       <c r="D47" t="n">
-        <v>49.97</v>
+        <v>51.68</v>
       </c>
     </row>
     <row r="48">
@@ -1181,13 +1193,13 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>9.449999999999999</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="C48" t="n">
-        <v>9.93</v>
+        <v>10.33</v>
       </c>
       <c r="D48" t="n">
-        <v>48.59</v>
+        <v>48.32</v>
       </c>
     </row>
     <row r="49">
@@ -1197,13 +1209,13 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>9.460000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="C49" t="n">
-        <v>9.960000000000001</v>
+        <v>10.24</v>
       </c>
       <c r="D49" t="n">
-        <v>50.48</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="50">
@@ -1213,13 +1225,13 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>9.52</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="C50" t="n">
-        <v>9.859999999999999</v>
+        <v>10.28</v>
       </c>
       <c r="D50" t="n">
-        <v>50.05</v>
+        <v>51.09</v>
       </c>
     </row>
     <row r="51">
@@ -1232,10 +1244,10 @@
         <v>9.49</v>
       </c>
       <c r="C51" t="n">
-        <v>9.75</v>
+        <v>9.98</v>
       </c>
       <c r="D51" t="n">
-        <v>50.03</v>
+        <v>49.54</v>
       </c>
     </row>
     <row r="52">
@@ -1245,13 +1257,13 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>9.460000000000001</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="C52" t="n">
-        <v>10.11</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="D52" t="n">
-        <v>48.63</v>
+        <v>51.75</v>
       </c>
     </row>
     <row r="53">
@@ -1261,13 +1273,13 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>9.5</v>
+        <v>9.52</v>
       </c>
       <c r="C53" t="n">
-        <v>10.12</v>
+        <v>10.36</v>
       </c>
       <c r="D53" t="n">
-        <v>49.05</v>
+        <v>50.81</v>
       </c>
     </row>
     <row r="54">
@@ -1277,13 +1289,13 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>9.539999999999999</v>
+        <v>9.48</v>
       </c>
       <c r="C54" t="n">
-        <v>9.67</v>
+        <v>10.38</v>
       </c>
       <c r="D54" t="n">
-        <v>51.04</v>
+        <v>49.91</v>
       </c>
     </row>
     <row r="55">
@@ -1293,13 +1305,13 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>9.470000000000001</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="C55" t="n">
-        <v>9.75</v>
+        <v>10.18</v>
       </c>
       <c r="D55" t="n">
-        <v>49.55</v>
+        <v>51.44</v>
       </c>
     </row>
     <row r="56">
@@ -1309,13 +1321,13 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>9.529999999999999</v>
+        <v>9.51</v>
       </c>
       <c r="C56" t="n">
-        <v>9.789999999999999</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="D56" t="n">
-        <v>49.36</v>
+        <v>50.27</v>
       </c>
     </row>
     <row r="57">
@@ -1325,13 +1337,13 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>9.539999999999999</v>
+        <v>9.52</v>
       </c>
       <c r="C57" t="n">
-        <v>9.710000000000001</v>
+        <v>10.05</v>
       </c>
       <c r="D57" t="n">
-        <v>49.34</v>
+        <v>48.43</v>
       </c>
     </row>
     <row r="58">
@@ -1341,13 +1353,13 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>9.460000000000001</v>
+        <v>9.52</v>
       </c>
       <c r="C58" t="n">
-        <v>10.38</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="D58" t="n">
-        <v>50</v>
+        <v>48.06</v>
       </c>
     </row>
     <row r="59">
@@ -1357,13 +1369,13 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>9.49</v>
+        <v>9.48</v>
       </c>
       <c r="C59" t="n">
-        <v>10.27</v>
+        <v>9.9</v>
       </c>
       <c r="D59" t="n">
-        <v>51.82</v>
+        <v>51.02</v>
       </c>
     </row>
     <row r="60">
@@ -1373,13 +1385,13 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>9.51</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="C60" t="n">
-        <v>10.19</v>
+        <v>9.52</v>
       </c>
       <c r="D60" t="n">
-        <v>49.28</v>
+        <v>48.08</v>
       </c>
     </row>
     <row r="61">
@@ -1392,10 +1404,10 @@
         <v>9.460000000000001</v>
       </c>
       <c r="C61" t="n">
-        <v>10.27</v>
+        <v>10.48</v>
       </c>
       <c r="D61" t="n">
-        <v>51.53</v>
+        <v>51.34</v>
       </c>
     </row>
   </sheetData>
